--- a/seed_data_template.xlsx
+++ b/seed_data_template.xlsx
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chờ nhập học</t>
+          <t>Kết quả hồ sơ</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Đã nộp học phí</t>
+          <t>Xử lý học phí</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1228,6 +1228,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -2912,7 +2913,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
